--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/62.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/62.xlsx
@@ -426,13 +426,13 @@
         <v>-3.383614940361592</v>
       </c>
       <c r="E2">
-        <v>-15.06903288003442</v>
+        <v>-10.99262689223593</v>
       </c>
       <c r="F2">
-        <v>-2.469256515597873</v>
+        <v>-2.173762124038636</v>
       </c>
       <c r="G2">
-        <v>-7.264820526599691</v>
+        <v>-7.240229923295995</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.833736120506994</v>
       </c>
       <c r="E3">
-        <v>-13.34881843461501</v>
+        <v>-12.42698410859004</v>
       </c>
       <c r="F3">
-        <v>-2.803902864083025</v>
+        <v>-2.301538624287863</v>
       </c>
       <c r="G3">
-        <v>-7.660330056941216</v>
+        <v>-6.520525961863796</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.502834131731761</v>
       </c>
       <c r="E4">
-        <v>-14.0382099824233</v>
+        <v>-11.83395536994043</v>
       </c>
       <c r="F4">
-        <v>-3.452416793121508</v>
+        <v>-2.330410541745036</v>
       </c>
       <c r="G4">
-        <v>-6.825774219456761</v>
+        <v>-6.361361917866574</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.469889036948147</v>
       </c>
       <c r="E5">
-        <v>-14.56521512064212</v>
+        <v>-13.05855049512275</v>
       </c>
       <c r="F5">
-        <v>-3.118124157517351</v>
+        <v>-2.50476034248186</v>
       </c>
       <c r="G5">
-        <v>-5.966841859725081</v>
+        <v>-5.982234809834285</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.685543085969567</v>
       </c>
       <c r="E6">
-        <v>-15.82504193749296</v>
+        <v>-13.64815283442938</v>
       </c>
       <c r="F6">
-        <v>-3.189246125986911</v>
+        <v>-2.291512065244377</v>
       </c>
       <c r="G6">
-        <v>-5.219492723817583</v>
+        <v>-5.943632340310084</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.120220690133961</v>
       </c>
       <c r="E7">
-        <v>-16.23270039508151</v>
+        <v>-14.15910996408906</v>
       </c>
       <c r="F7">
-        <v>-2.908388986435141</v>
+        <v>-2.108557183927273</v>
       </c>
       <c r="G7">
-        <v>-5.708485185733101</v>
+        <v>-5.651432584183502</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.710591055739613</v>
       </c>
       <c r="E8">
-        <v>-17.28050577379985</v>
+        <v>-15.45239505137272</v>
       </c>
       <c r="F8">
-        <v>-2.69362314011573</v>
+        <v>-1.867407835828698</v>
       </c>
       <c r="G8">
-        <v>-4.712149338171129</v>
+        <v>-5.610613592501447</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.393083280924556</v>
       </c>
       <c r="E9">
-        <v>-17.28921921115934</v>
+        <v>-15.49216620301928</v>
       </c>
       <c r="F9">
-        <v>-3.0288070990453</v>
+        <v>-1.697266969865499</v>
       </c>
       <c r="G9">
-        <v>-5.614884770652508</v>
+        <v>-5.379006607590013</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.094497753416131</v>
       </c>
       <c r="E10">
-        <v>-18.11619834373655</v>
+        <v>-16.43929773922378</v>
       </c>
       <c r="F10">
-        <v>-2.297217031547457</v>
+        <v>-1.677904710192463</v>
       </c>
       <c r="G10">
-        <v>-6.20308291628574</v>
+        <v>-5.176248350410383</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.742216687201083</v>
       </c>
       <c r="E11">
-        <v>-20.23115060631296</v>
+        <v>-17.295735599728</v>
       </c>
       <c r="F11">
-        <v>-2.453745335980452</v>
+        <v>-1.508813385728611</v>
       </c>
       <c r="G11">
-        <v>-4.410334209715478</v>
+        <v>-5.283931121815441</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.278695268208224</v>
       </c>
       <c r="E12">
-        <v>-20.12538492671488</v>
+        <v>-17.41785662552325</v>
       </c>
       <c r="F12">
-        <v>-1.728012654387805</v>
+        <v>-1.200351730845951</v>
       </c>
       <c r="G12">
-        <v>-6.300876187179662</v>
+        <v>-4.965882383492247</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.65551016206414</v>
       </c>
       <c r="E13">
-        <v>-21.46621597724517</v>
+        <v>-18.94280368729452</v>
       </c>
       <c r="F13">
-        <v>-1.939065758007869</v>
+        <v>-1.298874436265313</v>
       </c>
       <c r="G13">
-        <v>-4.926710771647183</v>
+        <v>-4.748838131910044</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.859998357700166</v>
       </c>
       <c r="E14">
-        <v>-22.63240033835511</v>
+        <v>-18.85289496853464</v>
       </c>
       <c r="F14">
-        <v>-1.745239382896424</v>
+        <v>-0.9424370548821165</v>
       </c>
       <c r="G14">
-        <v>-5.47685992560953</v>
+        <v>-4.720467170438416</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.890684155543366</v>
       </c>
       <c r="E15">
-        <v>-22.51026269971455</v>
+        <v>-19.70435312866039</v>
       </c>
       <c r="F15">
-        <v>-1.467953335218123</v>
+        <v>-0.8183625285560009</v>
       </c>
       <c r="G15">
-        <v>-5.56986248017876</v>
+        <v>-4.312778516579348</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.782457156645974</v>
       </c>
       <c r="E16">
-        <v>-22.28948629210931</v>
+        <v>-20.23175697516639</v>
       </c>
       <c r="F16">
-        <v>-1.954258016175212</v>
+        <v>-0.1301582037797829</v>
       </c>
       <c r="G16">
-        <v>-5.21235755885007</v>
+        <v>-4.27205090095798</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.574531445544043</v>
       </c>
       <c r="E17">
-        <v>-24.28173607930499</v>
+        <v>-21.2857298727021</v>
       </c>
       <c r="F17">
-        <v>-1.211597646706357</v>
+        <v>-0.1153279421674633</v>
       </c>
       <c r="G17">
-        <v>-5.192972780261054</v>
+        <v>-4.073736131072424</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.322315613521954</v>
       </c>
       <c r="E18">
-        <v>-25.03610461829022</v>
+        <v>-22.03424653693065</v>
       </c>
       <c r="F18">
-        <v>-1.074845785647798</v>
+        <v>0.4021871374249026</v>
       </c>
       <c r="G18">
-        <v>-5.263943261225878</v>
+        <v>-3.878802275432359</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.070537812621969</v>
       </c>
       <c r="E19">
-        <v>-25.91275615831238</v>
+        <v>-23.48355531405414</v>
       </c>
       <c r="F19">
-        <v>-0.3885450491632131</v>
+        <v>0.3948983326476698</v>
       </c>
       <c r="G19">
-        <v>-4.755062147015258</v>
+        <v>-3.551566326893038</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.858833148697469</v>
       </c>
       <c r="E20">
-        <v>-26.87939948132093</v>
+        <v>-23.621986000722</v>
       </c>
       <c r="F20">
-        <v>0.06033399253539424</v>
+        <v>0.692353469849333</v>
       </c>
       <c r="G20">
-        <v>-3.617968004823414</v>
+        <v>-3.651466468671988</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.718968737168187</v>
       </c>
       <c r="E21">
-        <v>-26.97899348889031</v>
+        <v>-24.08991170784514</v>
       </c>
       <c r="F21">
-        <v>-0.6395246332308101</v>
+        <v>1.019351502104438</v>
       </c>
       <c r="G21">
-        <v>-3.346408795434174</v>
+        <v>-3.480204234239547</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.667426936116134</v>
       </c>
       <c r="E22">
-        <v>-28.49700468774912</v>
+        <v>-24.82258387086946</v>
       </c>
       <c r="F22">
-        <v>0.1930285100550415</v>
+        <v>1.413415816024996</v>
       </c>
       <c r="G22">
-        <v>-3.773949551164068</v>
+        <v>-3.350763517412151</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.722323364178027</v>
       </c>
       <c r="E23">
-        <v>-27.93233407602543</v>
+        <v>-25.66337243110173</v>
       </c>
       <c r="F23">
-        <v>0.2513223809248483</v>
+        <v>1.406134466554389</v>
       </c>
       <c r="G23">
-        <v>-4.279611617293845</v>
+        <v>-3.26842585449762</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.874136577717762</v>
       </c>
       <c r="E24">
-        <v>-28.55434807651103</v>
+        <v>-25.36082759893327</v>
       </c>
       <c r="F24">
-        <v>1.245921583913742</v>
+        <v>1.731449256247005</v>
       </c>
       <c r="G24">
-        <v>-3.678568608272335</v>
+        <v>-2.814059698094037</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.128789410949152</v>
       </c>
       <c r="E25">
-        <v>-27.43579689608556</v>
+        <v>-26.14514494478184</v>
       </c>
       <c r="F25">
-        <v>0.4018996939361312</v>
+        <v>1.786986320400295</v>
       </c>
       <c r="G25">
-        <v>-3.903502530008882</v>
+        <v>-3.003837333166653</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.458446803463078</v>
       </c>
       <c r="E26">
-        <v>-28.54717132734173</v>
+        <v>-26.4974037165085</v>
       </c>
       <c r="F26">
-        <v>0.8476475068521564</v>
+        <v>2.383467179399329</v>
       </c>
       <c r="G26">
-        <v>-4.09628774285046</v>
+        <v>-3.400464262193174</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.859817750500139</v>
       </c>
       <c r="E27">
-        <v>-29.55884792074539</v>
+        <v>-26.22809288136131</v>
       </c>
       <c r="F27">
-        <v>1.00637098490257</v>
+        <v>2.054409825780865</v>
       </c>
       <c r="G27">
-        <v>-4.485972702009212</v>
+        <v>-3.456856345361222</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.305096495692675</v>
       </c>
       <c r="E28">
-        <v>-29.36074181715673</v>
+        <v>-26.42424905223297</v>
       </c>
       <c r="F28">
-        <v>0.957959537148161</v>
+        <v>2.25215106523794</v>
       </c>
       <c r="G28">
-        <v>-4.558350374308645</v>
+        <v>-3.265901264478013</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.787611632045799</v>
       </c>
       <c r="E29">
-        <v>-29.88151090857131</v>
+        <v>-26.09438439596978</v>
       </c>
       <c r="F29">
-        <v>1.773084658646514</v>
+        <v>2.016866558351186</v>
       </c>
       <c r="G29">
-        <v>-5.376025137266963</v>
+        <v>-3.035069670710141</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.287777901725283</v>
       </c>
       <c r="E30">
-        <v>-30.18039883816826</v>
+        <v>-25.86226141502512</v>
       </c>
       <c r="F30">
-        <v>0.9716607339904647</v>
+        <v>1.943675328109433</v>
       </c>
       <c r="G30">
-        <v>-4.584872928609766</v>
+        <v>-3.484574620685071</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.793055274961464</v>
       </c>
       <c r="E31">
-        <v>-27.80370496808417</v>
+        <v>-25.46519779952621</v>
       </c>
       <c r="F31">
-        <v>1.54066464623864</v>
+        <v>2.062191509162763</v>
       </c>
       <c r="G31">
-        <v>-4.856312043747813</v>
+        <v>-3.79752196407723</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.29066878571833</v>
       </c>
       <c r="E32">
-        <v>-29.05872444282652</v>
+        <v>-25.40595639318886</v>
       </c>
       <c r="F32">
-        <v>0.09377849805602148</v>
+        <v>1.819696892402042</v>
       </c>
       <c r="G32">
-        <v>-4.386101278420765</v>
+        <v>-3.86442751571369</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.761187137878682</v>
       </c>
       <c r="E33">
-        <v>-26.01413189354012</v>
+        <v>-25.24521050207269</v>
       </c>
       <c r="F33">
-        <v>0.2688423514940578</v>
+        <v>1.718450514962275</v>
       </c>
       <c r="G33">
-        <v>-4.115860495050037</v>
+        <v>-3.731498844112566</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.19605015952486</v>
       </c>
       <c r="E34">
-        <v>-27.96405215091315</v>
+        <v>-24.8840638581109</v>
       </c>
       <c r="F34">
-        <v>0.7177131095186371</v>
+        <v>1.609107674527546</v>
       </c>
       <c r="G34">
-        <v>-4.124502059646622</v>
+        <v>-3.724914546253778</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.56841822945219</v>
       </c>
       <c r="E35">
-        <v>-26.34916729790272</v>
+        <v>-24.10751301743976</v>
       </c>
       <c r="F35">
-        <v>0.1788012999119599</v>
+        <v>1.708468687758541</v>
       </c>
       <c r="G35">
-        <v>-4.210591362538582</v>
+        <v>-3.676396468772529</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.87204135021927</v>
       </c>
       <c r="E36">
-        <v>-26.030304498439</v>
+        <v>-24.17863260816612</v>
       </c>
       <c r="F36">
-        <v>-0.05282762162624063</v>
+        <v>1.590570468787698</v>
       </c>
       <c r="G36">
-        <v>-4.742428753938861</v>
+        <v>-3.502212811142632</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.07782743901944</v>
       </c>
       <c r="E37">
-        <v>-26.14922339830282</v>
+        <v>-23.7333751284539</v>
       </c>
       <c r="F37">
-        <v>0.2392182764351419</v>
+        <v>1.293486440182489</v>
       </c>
       <c r="G37">
-        <v>-5.242031281872664</v>
+        <v>-3.51648836256684</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.1825419829476</v>
       </c>
       <c r="E38">
-        <v>-27.77511010811272</v>
+        <v>-23.16329703558529</v>
       </c>
       <c r="F38">
-        <v>1.100944034545384</v>
+        <v>1.424244234714391</v>
       </c>
       <c r="G38">
-        <v>-4.272374633287279</v>
+        <v>-3.26479169802679</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.16605435816828</v>
       </c>
       <c r="E39">
-        <v>-25.9395734438368</v>
+        <v>-22.32153662390301</v>
       </c>
       <c r="F39">
-        <v>1.391957786822878</v>
+        <v>0.9125268985742192</v>
       </c>
       <c r="G39">
-        <v>-3.46194207582471</v>
+        <v>-3.021344986394658</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.03170661450123</v>
       </c>
       <c r="E40">
-        <v>-25.64830458041525</v>
+        <v>-21.82776548270547</v>
       </c>
       <c r="F40">
-        <v>0.5060942309624614</v>
+        <v>1.360401958980634</v>
       </c>
       <c r="G40">
-        <v>-3.828942275231278</v>
+        <v>-2.840216748152401</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.77791092049102</v>
       </c>
       <c r="E41">
-        <v>-23.95707124362049</v>
+        <v>-21.93962807652841</v>
       </c>
       <c r="F41">
-        <v>-0.3872834456087494</v>
+        <v>0.9931055093141383</v>
       </c>
       <c r="G41">
-        <v>-4.005995141166808</v>
+        <v>-2.895530593804318</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.41855862048766</v>
       </c>
       <c r="E42">
-        <v>-23.69516143105416</v>
+        <v>-21.40963677936704</v>
       </c>
       <c r="F42">
-        <v>0.2023418447647163</v>
+        <v>0.8768110096351157</v>
       </c>
       <c r="G42">
-        <v>-3.27679851240132</v>
+        <v>-2.82185277069851</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.973045503149901</v>
       </c>
       <c r="E43">
-        <v>-23.26313608262284</v>
+        <v>-20.27626278772325</v>
       </c>
       <c r="F43">
-        <v>0.2160604373224789</v>
+        <v>0.6237099766489492</v>
       </c>
       <c r="G43">
-        <v>-3.110011094198048</v>
+        <v>-2.512795436747111</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.462418458115851</v>
       </c>
       <c r="E44">
-        <v>-23.28737837712587</v>
+        <v>-19.59365758721973</v>
       </c>
       <c r="F44">
-        <v>-0.1193272999881793</v>
+        <v>0.3855609752833137</v>
       </c>
       <c r="G44">
-        <v>-3.682124442405431</v>
+        <v>-2.651637444847106</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.921020657028118</v>
       </c>
       <c r="E45">
-        <v>-23.82109510484561</v>
+        <v>-19.70414131488282</v>
       </c>
       <c r="F45">
-        <v>-0.3421689001174827</v>
+        <v>0.6169919170122452</v>
       </c>
       <c r="G45">
-        <v>-3.296681943207239</v>
+        <v>-2.250018772162376</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.366668748738217</v>
       </c>
       <c r="E46">
-        <v>-23.84792069679268</v>
+        <v>-19.98132248549055</v>
       </c>
       <c r="F46">
-        <v>0.104650820217765</v>
+        <v>0.2787164909354279</v>
       </c>
       <c r="G46">
-        <v>-3.937478760117631</v>
+        <v>-2.173262881183645</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.838464241658637</v>
       </c>
       <c r="E47">
-        <v>-23.6564618079294</v>
+        <v>-18.5993829492671</v>
       </c>
       <c r="F47">
-        <v>-0.3538455670273445</v>
+        <v>0.3863959696253356</v>
       </c>
       <c r="G47">
-        <v>-3.431942009728227</v>
+        <v>-2.343702731069885</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.346465973405449</v>
       </c>
       <c r="E48">
-        <v>-21.68765274545106</v>
+        <v>-18.54951118767856</v>
       </c>
       <c r="F48">
-        <v>-0.3076292928903546</v>
+        <v>0.4976788465174212</v>
       </c>
       <c r="G48">
-        <v>-3.803484904723332</v>
+        <v>-2.035091834443566</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.92374906007133</v>
       </c>
       <c r="E49">
-        <v>-21.10979568777104</v>
+        <v>-17.44624382492846</v>
       </c>
       <c r="F49">
-        <v>-0.6509685289004853</v>
+        <v>0.3565913104726094</v>
       </c>
       <c r="G49">
-        <v>-3.832709579676254</v>
+        <v>-2.553483891199611</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.571824394421865</v>
       </c>
       <c r="E50">
-        <v>-20.21542654823716</v>
+        <v>-17.45643580551959</v>
       </c>
       <c r="F50">
-        <v>-0.6234021184701233</v>
+        <v>0.3445642441513634</v>
       </c>
       <c r="G50">
-        <v>-4.203158572687683</v>
+        <v>-2.240197151010608</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.308352613090452</v>
       </c>
       <c r="E51">
-        <v>-22.0450282735299</v>
+        <v>-16.59533388869758</v>
       </c>
       <c r="F51">
-        <v>-0.7311950834942146</v>
+        <v>0.2799524151004048</v>
       </c>
       <c r="G51">
-        <v>-2.87773575867129</v>
+        <v>-2.317477801652152</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.128377431064142</v>
       </c>
       <c r="E52">
-        <v>-20.47738204612807</v>
+        <v>-16.27722282048367</v>
       </c>
       <c r="F52">
-        <v>-0.6609006540600513</v>
+        <v>0.1187537752504266</v>
       </c>
       <c r="G52">
-        <v>-3.547592773625364</v>
+        <v>-2.339329733879771</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.031966546940944</v>
       </c>
       <c r="E53">
-        <v>-18.87277639114659</v>
+        <v>-16.33379786515048</v>
       </c>
       <c r="F53">
-        <v>-1.150043321739131</v>
+        <v>-0.04001691974194627</v>
       </c>
       <c r="G53">
-        <v>-3.673728287800411</v>
+        <v>-2.403465285505059</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.011571687672641</v>
       </c>
       <c r="E54">
-        <v>-20.16184181572422</v>
+        <v>-15.77050611958664</v>
       </c>
       <c r="F54">
-        <v>-0.882960275361112</v>
+        <v>0.1310947928173336</v>
       </c>
       <c r="G54">
-        <v>-3.189539595932541</v>
+        <v>-2.434133702216867</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.053802889117949</v>
       </c>
       <c r="E55">
-        <v>-20.36582678994318</v>
+        <v>-15.2669666253531</v>
       </c>
       <c r="F55">
-        <v>-0.7354379813313536</v>
+        <v>-0.1476657488379504</v>
       </c>
       <c r="G55">
-        <v>-3.450141510272878</v>
+        <v>-2.717691893746863</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.154708176589925</v>
       </c>
       <c r="E56">
-        <v>-16.39783623056801</v>
+        <v>-15.05210854388575</v>
       </c>
       <c r="F56">
-        <v>-0.5968960183153447</v>
+        <v>-0.1093148231905417</v>
       </c>
       <c r="G56">
-        <v>-3.350473724762537</v>
+        <v>-2.439597990646067</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.295145966933774</v>
       </c>
       <c r="E57">
-        <v>-18.59594824350147</v>
+        <v>-14.9236995561447</v>
       </c>
       <c r="F57">
-        <v>-1.01748382810614</v>
+        <v>-0.2576422903358212</v>
       </c>
       <c r="G57">
-        <v>-3.33021956822468</v>
+        <v>-3.037745683916032</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.478992898848413</v>
       </c>
       <c r="E58">
-        <v>-17.24087167812701</v>
+        <v>-14.75687336364898</v>
       </c>
       <c r="F58">
-        <v>-0.8226435312936687</v>
+        <v>-0.1660082882381399</v>
       </c>
       <c r="G58">
-        <v>-3.410413809829907</v>
+        <v>-3.064578916823494</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.68658155479891</v>
       </c>
       <c r="E59">
-        <v>-18.2168721862504</v>
+        <v>-14.22557795813162</v>
       </c>
       <c r="F59">
-        <v>-1.315592547188613</v>
+        <v>-0.3980364828644898</v>
       </c>
       <c r="G59">
-        <v>-3.741866110883877</v>
+        <v>-3.119884930241638</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.926312770465013</v>
       </c>
       <c r="E60">
-        <v>-18.60412591660006</v>
+        <v>-14.08110434898613</v>
       </c>
       <c r="F60">
-        <v>-1.784698664128778</v>
+        <v>-0.1048996249336203</v>
       </c>
       <c r="G60">
-        <v>-3.662157467772597</v>
+        <v>-3.506700681094756</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.182212215145803</v>
       </c>
       <c r="E61">
-        <v>-16.9474016127033</v>
+        <v>-13.50815223388074</v>
       </c>
       <c r="F61">
-        <v>-0.584016561936618</v>
+        <v>-0.5078084176138691</v>
       </c>
       <c r="G61">
-        <v>-4.202612927068141</v>
+        <v>-3.417773498832255</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.461374544026599</v>
       </c>
       <c r="E62">
-        <v>-19.49149274184027</v>
+        <v>-12.71045324114357</v>
       </c>
       <c r="F62">
-        <v>-1.13454373926535</v>
+        <v>-0.4334740403562526</v>
       </c>
       <c r="G62">
-        <v>-3.527701510585671</v>
+        <v>-3.605942915236746</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.753866366597738</v>
       </c>
       <c r="E63">
-        <v>-16.95678371708609</v>
+        <v>-13.30488161200965</v>
       </c>
       <c r="F63">
-        <v>-1.425550864603622</v>
+        <v>-0.7079751168263416</v>
       </c>
       <c r="G63">
-        <v>-3.387246062328368</v>
+        <v>-3.699974103174873</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.060499421225575</v>
       </c>
       <c r="E64">
-        <v>-15.04753170500578</v>
+        <v>-13.1001449065409</v>
       </c>
       <c r="F64">
-        <v>-1.667405981729382</v>
+        <v>-0.9025884409704462</v>
       </c>
       <c r="G64">
-        <v>-3.803839965987724</v>
+        <v>-3.857341954893408</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.377563037200087</v>
       </c>
       <c r="E65">
-        <v>-16.43771536570902</v>
+        <v>-12.39595961999358</v>
       </c>
       <c r="F65">
-        <v>-0.8547932985637204</v>
+        <v>-0.8958562990878947</v>
       </c>
       <c r="G65">
-        <v>-4.747167255371732</v>
+        <v>-3.96067000432049</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.698751166206788</v>
       </c>
       <c r="E66">
-        <v>-16.8674273754324</v>
+        <v>-12.65854225279453</v>
       </c>
       <c r="F66">
-        <v>-1.46303780304991</v>
+        <v>-1.085734675157597</v>
       </c>
       <c r="G66">
-        <v>-4.744358094191694</v>
+        <v>-3.864367468588094</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.025163176342543</v>
       </c>
       <c r="E67">
-        <v>-15.8271226963667</v>
+        <v>-12.61966404158282</v>
       </c>
       <c r="F67">
-        <v>-1.761349472146069</v>
+        <v>-0.8190127969671985</v>
       </c>
       <c r="G67">
-        <v>-5.177960998862153</v>
+        <v>-4.541633776691747</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.342546957609111</v>
       </c>
       <c r="E68">
-        <v>-15.93265994934192</v>
+        <v>-12.69749937502143</v>
       </c>
       <c r="F68">
-        <v>-1.824329417413512</v>
+        <v>-0.9380939245892387</v>
       </c>
       <c r="G68">
-        <v>-4.590663560112855</v>
+        <v>-4.4182891484846</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.655254427067181</v>
       </c>
       <c r="E69">
-        <v>-15.66287564810371</v>
+        <v>-11.94044370830903</v>
       </c>
       <c r="F69">
-        <v>-2.220382641468192</v>
+        <v>-1.23366369758213</v>
       </c>
       <c r="G69">
-        <v>-4.383331278409593</v>
+        <v>-4.339342842793926</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.941507602062185</v>
       </c>
       <c r="E70">
-        <v>-16.26336770750404</v>
+        <v>-12.32483172284456</v>
       </c>
       <c r="F70">
-        <v>-1.637473753996625</v>
+        <v>-1.436472888809533</v>
       </c>
       <c r="G70">
-        <v>-4.578090214162053</v>
+        <v>-4.219809901689803</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.20477460626745</v>
       </c>
       <c r="E71">
-        <v>-15.50520313336792</v>
+        <v>-12.03996295807457</v>
       </c>
       <c r="F71">
-        <v>-2.029964169851864</v>
+        <v>-1.360102384475836</v>
       </c>
       <c r="G71">
-        <v>-4.084868346008931</v>
+        <v>-4.226365481358089</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.42142161847708</v>
       </c>
       <c r="E72">
-        <v>-14.83173084456769</v>
+        <v>-11.56491864674068</v>
       </c>
       <c r="F72">
-        <v>-1.884607228213024</v>
+        <v>-1.195030298650367</v>
       </c>
       <c r="G72">
-        <v>-5.322329953261535</v>
+        <v>-4.198662870501786</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.59283757431423</v>
       </c>
       <c r="E73">
-        <v>-15.44223629647219</v>
+        <v>-12.75716440891391</v>
       </c>
       <c r="F73">
-        <v>-2.245495427651462</v>
+        <v>-1.368220385023271</v>
       </c>
       <c r="G73">
-        <v>-4.500820006498873</v>
+        <v>-4.379744115341404</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.7033636757282</v>
       </c>
       <c r="E74">
-        <v>-16.95172095248112</v>
+        <v>-12.75668678961156</v>
       </c>
       <c r="F74">
-        <v>-2.342892381770419</v>
+        <v>-1.383939484858794</v>
       </c>
       <c r="G74">
-        <v>-5.682166269510089</v>
+        <v>-3.859835215977922</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.75309174799693</v>
       </c>
       <c r="E75">
-        <v>-15.14571777393606</v>
+        <v>-12.60840053246988</v>
       </c>
       <c r="F75">
-        <v>-1.925058065226529</v>
+        <v>-1.510755078920773</v>
       </c>
       <c r="G75">
-        <v>-4.029131559733254</v>
+        <v>-4.036846309999993</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.73977168669928</v>
       </c>
       <c r="E76">
-        <v>-15.97044586597521</v>
+        <v>-14.03933965590366</v>
       </c>
       <c r="F76">
-        <v>-2.707469301253524</v>
+        <v>-1.875309632484002</v>
       </c>
       <c r="G76">
-        <v>-4.289482842592844</v>
+        <v>-3.931129429272043</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.66324556249634</v>
       </c>
       <c r="E77">
-        <v>-17.12767590346881</v>
+        <v>-14.04709785465844</v>
       </c>
       <c r="F77">
-        <v>-2.390144115160909</v>
+        <v>-1.881809003126367</v>
       </c>
       <c r="G77">
-        <v>-3.665747241585378</v>
+        <v>-3.553148438115253</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.53142470137015</v>
       </c>
       <c r="E78">
-        <v>-16.74035987494927</v>
+        <v>-14.63557052048472</v>
       </c>
       <c r="F78">
-        <v>-2.158534246072973</v>
+        <v>-1.981208949625294</v>
       </c>
       <c r="G78">
-        <v>-2.992188190801105</v>
+        <v>-3.285090237222696</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.34029687671906</v>
       </c>
       <c r="E79">
-        <v>-18.76393318195681</v>
+        <v>-14.0351656785222</v>
       </c>
       <c r="F79">
-        <v>-2.095002608115264</v>
+        <v>-1.650981112866674</v>
       </c>
       <c r="G79">
-        <v>-3.104322281734012</v>
+        <v>-2.783662798819705</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.10646128909896</v>
       </c>
       <c r="E80">
-        <v>-18.66336732293741</v>
+        <v>-14.88278211817249</v>
       </c>
       <c r="F80">
-        <v>-2.361215040352942</v>
+        <v>-1.802940971073229</v>
       </c>
       <c r="G80">
-        <v>-2.741441837292221</v>
+        <v>-2.506373005052972</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.823770870602239</v>
       </c>
       <c r="E81">
-        <v>-20.45416974803361</v>
+        <v>-15.88761837252415</v>
       </c>
       <c r="F81">
-        <v>-3.231667649051676</v>
+        <v>-1.987567497809183</v>
       </c>
       <c r="G81">
-        <v>-3.143843733354285</v>
+        <v>-2.530987105057988</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.515665711006868</v>
       </c>
       <c r="E82">
-        <v>-18.95044559613221</v>
+        <v>-16.83270237554551</v>
       </c>
       <c r="F82">
-        <v>-2.179482000954966</v>
+        <v>-1.786000857685979</v>
       </c>
       <c r="G82">
-        <v>-2.039164596005703</v>
+        <v>-2.456327641985921</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.179447607448424</v>
       </c>
       <c r="E83">
-        <v>-20.92933865570724</v>
+        <v>-17.99031035526967</v>
       </c>
       <c r="F83">
-        <v>-2.995939965604424</v>
+        <v>-1.996592560662683</v>
       </c>
       <c r="G83">
-        <v>-1.977545802166247</v>
+        <v>-2.112406424764795</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.84051086638342</v>
       </c>
       <c r="E84">
-        <v>-22.14018665140438</v>
+        <v>-18.41946168146421</v>
       </c>
       <c r="F84">
-        <v>-2.622756308806232</v>
+        <v>-1.85751381556966</v>
       </c>
       <c r="G84">
-        <v>-2.887137049943889</v>
+        <v>-2.024763728841122</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.504160482300522</v>
       </c>
       <c r="E85">
-        <v>-20.88777746997968</v>
+        <v>-20.09424414820132</v>
       </c>
       <c r="F85">
-        <v>-2.60539538477836</v>
+        <v>-2.008999847621814</v>
       </c>
       <c r="G85">
-        <v>-1.657196997858282</v>
+        <v>-2.0626090824339</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.191956424366541</v>
       </c>
       <c r="E86">
-        <v>-22.94312284362215</v>
+        <v>-20.30382349807481</v>
       </c>
       <c r="F86">
-        <v>-2.413879326353323</v>
+        <v>-1.751714730884107</v>
       </c>
       <c r="G86">
-        <v>-2.636918066842409</v>
+        <v>-1.744069524127577</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.917151774466436</v>
       </c>
       <c r="E87">
-        <v>-24.64491779681595</v>
+        <v>-21.96654919233594</v>
       </c>
       <c r="F87">
-        <v>-3.121739152863168</v>
+        <v>-2.106625431143944</v>
       </c>
       <c r="G87">
-        <v>-2.117860270215631</v>
+        <v>-1.66767391590242</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.693832799244251</v>
       </c>
       <c r="E88">
-        <v>-26.07199443371763</v>
+        <v>-22.71205893156532</v>
       </c>
       <c r="F88">
-        <v>-3.464007309821479</v>
+        <v>-1.911753656370166</v>
       </c>
       <c r="G88">
-        <v>-3.044922620797003</v>
+        <v>-1.645093585933881</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.541050577896489</v>
       </c>
       <c r="E89">
-        <v>-26.72033148757999</v>
+        <v>-23.81014308658203</v>
       </c>
       <c r="F89">
-        <v>-2.979353565098169</v>
+        <v>-1.969210876163146</v>
       </c>
       <c r="G89">
-        <v>-0.9552043277321954</v>
+        <v>-1.620646573582696</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.461543034495136</v>
       </c>
       <c r="E90">
-        <v>-28.02531201795437</v>
+        <v>-26.05315131393689</v>
       </c>
       <c r="F90">
-        <v>-2.076798406071342</v>
+        <v>-2.086016478529696</v>
       </c>
       <c r="G90">
-        <v>-1.199322000724243</v>
+        <v>-1.475483952827615</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.477442907226356</v>
       </c>
       <c r="E91">
-        <v>-30.2765207610701</v>
+        <v>-27.79416919488236</v>
       </c>
       <c r="F91">
-        <v>-3.031307111866949</v>
+        <v>-1.985755029931857</v>
       </c>
       <c r="G91">
-        <v>-1.958471702183573</v>
+        <v>-1.868894444517885</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.578766463621496</v>
       </c>
       <c r="E92">
-        <v>-30.09101757724663</v>
+        <v>-30.17931069680116</v>
       </c>
       <c r="F92">
-        <v>-2.897893571441672</v>
+        <v>-1.641385304872644</v>
       </c>
       <c r="G92">
-        <v>-3.390519936045624</v>
+        <v>-1.710487516452087</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.785372186031229</v>
       </c>
       <c r="E93">
-        <v>-32.94199779759783</v>
+        <v>-31.05933049120775</v>
       </c>
       <c r="F93">
-        <v>-2.428558825098333</v>
+        <v>-2.123222600426435</v>
       </c>
       <c r="G93">
-        <v>-2.735609433875674</v>
+        <v>-2.136172032777699</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.077076005074073</v>
       </c>
       <c r="E94">
-        <v>-34.24280642719641</v>
+        <v>-33.00845125540075</v>
       </c>
       <c r="F94">
-        <v>-3.024854958166543</v>
+        <v>-1.929318358779127</v>
       </c>
       <c r="G94">
-        <v>-2.57646366509059</v>
+        <v>-2.022458441367169</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.461073114614564</v>
       </c>
       <c r="E95">
-        <v>-35.32773943855306</v>
+        <v>-35.21498182768963</v>
       </c>
       <c r="F95">
-        <v>-3.035271678256747</v>
+        <v>-1.83013710127454</v>
       </c>
       <c r="G95">
-        <v>-2.955622102057973</v>
+        <v>-2.600730536064988</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.917287489900392</v>
       </c>
       <c r="E96">
-        <v>-38.34237072134215</v>
+        <v>-36.5913789034001</v>
       </c>
       <c r="F96">
-        <v>-3.280050103946987</v>
+        <v>-1.83039472353681</v>
       </c>
       <c r="G96">
-        <v>-3.450595779831731</v>
+        <v>-2.716926945581667</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.432730002927444</v>
       </c>
       <c r="E97">
-        <v>-40.90278397098569</v>
+        <v>-39.47997683532594</v>
       </c>
       <c r="F97">
-        <v>-2.86631206420994</v>
+        <v>-1.82480821377233</v>
       </c>
       <c r="G97">
-        <v>-4.331207762648016</v>
+        <v>-2.760155654521321</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.997092676080801</v>
       </c>
       <c r="E98">
-        <v>-43.27710220419199</v>
+        <v>-41.61424983698545</v>
       </c>
       <c r="F98">
-        <v>-2.265160869793922</v>
+        <v>-2.034560780569999</v>
       </c>
       <c r="G98">
-        <v>-4.457340666078473</v>
+        <v>-3.719411096655711</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.57676154645386</v>
       </c>
       <c r="E99">
-        <v>-43.84136372460018</v>
+        <v>-43.5498643579501</v>
       </c>
       <c r="F99">
-        <v>-2.583291229002058</v>
+        <v>-1.959838727367872</v>
       </c>
       <c r="G99">
-        <v>-4.81756337252651</v>
+        <v>-3.302819803740946</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.18315287104505</v>
       </c>
       <c r="E100">
-        <v>-45.94219299206652</v>
+        <v>-46.03565062990346</v>
       </c>
       <c r="F100">
-        <v>-2.580776305567159</v>
+        <v>-1.800878336240258</v>
       </c>
       <c r="G100">
-        <v>-4.551053343176484</v>
+        <v>-3.878572529908341</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.75322406008431</v>
       </c>
       <c r="E101">
-        <v>-48.63474585152364</v>
+        <v>-47.68226913234408</v>
       </c>
       <c r="F101">
-        <v>-2.200484428085545</v>
+        <v>-1.709626211515267</v>
       </c>
       <c r="G101">
-        <v>-5.057587397999693</v>
+        <v>-4.315070750330345</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.35002201854061</v>
       </c>
       <c r="E102">
-        <v>-50.24918319601382</v>
+        <v>-50.52344050584887</v>
       </c>
       <c r="F102">
-        <v>-2.819224347565205</v>
+        <v>-2.016977854078176</v>
       </c>
       <c r="G102">
-        <v>-5.364456927983739</v>
+        <v>-4.49114980853339</v>
       </c>
     </row>
   </sheetData>
